--- a/src/testData/opencarttestdata.xlsx
+++ b/src/testData/opencarttestdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StudyMaterial\PW_Sample_Project\src\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18280E4-3E00-4D77-B323-CF30145D8232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8FDE2E-9B32-4472-BD5D-046F989CD316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="2080" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>pw1234</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>password</t>
   </si>
@@ -371,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.453125" customWidth="1"/>
@@ -380,35 +377,30 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{8C2871BE-C1DE-46BE-8F4E-AAECD9CC3452}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{386C66EE-B858-4844-96BF-611BE6C602FE}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{CAF1F92A-9EDB-448C-A8B2-81B593A007BF}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{CAF1F92A-9EDB-448C-A8B2-81B593A007BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
